--- a/request_forms/015_research_publication_support_request_form--request_forms.xlsx
+++ b/request_forms/015_research_publication_support_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1186,8 +1186,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'research_assistant'}</t>
+          <t>research_assistant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Research Assistant'}</t>
+          <t>Research Assistant</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'research_associate'}</t>
+          <t>research_associate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Research Associate'}</t>
+          <t>Research Associate</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'mary_smith'}</t>
+          <t>mary_smith</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Mary Smith'}</t>
+          <t>Mary Smith</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'pdf'}</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'PDF'}</t>
+          <t>PDF</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'docx'}</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'DOCX'}</t>
+          <t>DOCX</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'doc'}</t>
+          <t>doc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'DOC'}</t>
+          <t>DOC</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'journal'}</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'journal'}</t>
+          <t>journal</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'book_chapter'}</t>
+          <t>book_chapter</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'book chapter'}</t>
+          <t>book chapter</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'april'}</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'April'}</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'may'}</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'May'}</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'june'}</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'June'}</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'july'}</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'July'}</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'august'}</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'August'}</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'september'}</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'September'}</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'october'}</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'October'}</t>
+          <t>October</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'november'}</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'November'}</t>
+          <t>November</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'december'}</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'December'}</t>
+          <t>December</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_2022}</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 2022}</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_2023}</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 2023}</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_2024}</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 2024}</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_2025}</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 2025}</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'submitted'}</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'submitted'}</t>
+          <t>submitted</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'in_review'}</t>
+          <t>in_review</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'in review'}</t>
+          <t>in review</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'in_production'}</t>
+          <t>in_production</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'in production'}</t>
+          <t>in production</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'research'}</t>
+          <t>research</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Research'}</t>
+          <t>Research</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'review'}</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Review'}</t>
+          <t>Review</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'research'}</t>
+          <t>research</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Research'}</t>
+          <t>Research</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'review'}</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'Review'}</t>
+          <t>Review</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
